--- a/output/Jiangxi/抚州市_api_news.xlsx
+++ b/output/Jiangxi/抚州市_api_news.xlsx
@@ -570,9 +570,7 @@
       <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/4870</t>
@@ -644,9 +642,7 @@
       <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/4836</t>
@@ -714,9 +710,7 @@
       <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/7462</t>
@@ -788,9 +782,7 @@
       <c r="M5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/6135</t>
@@ -862,9 +854,7 @@
       <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/6381</t>
@@ -936,9 +926,7 @@
       <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/6136</t>
@@ -1010,9 +998,7 @@
       <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/6397</t>
@@ -1084,9 +1070,7 @@
       <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/6528</t>
@@ -1158,9 +1142,7 @@
       <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/6330</t>
@@ -1232,9 +1214,7 @@
       <c r="M11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/6266</t>
@@ -1306,9 +1286,7 @@
       <c r="M12" t="n">
         <v>0</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/6273</t>
@@ -1380,9 +1358,7 @@
       <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/6280</t>
@@ -1454,9 +1430,7 @@
       <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/6340</t>
@@ -1528,9 +1502,7 @@
       <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/6101</t>
@@ -1602,9 +1574,7 @@
       <c r="M16" t="n">
         <v>0</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/6361</t>
@@ -1676,9 +1646,7 @@
       <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/6363</t>
@@ -1750,9 +1718,7 @@
       <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/6373</t>
@@ -1824,9 +1790,7 @@
       <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/6389</t>
@@ -1898,9 +1862,7 @@
       <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/6392</t>
@@ -1972,9 +1934,7 @@
       <c r="M21" t="n">
         <v>0</v>
       </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/6186</t>
@@ -2046,9 +2006,7 @@
       <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/6449</t>
@@ -2120,9 +2078,7 @@
       <c r="M23" t="n">
         <v>0</v>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/6491</t>
@@ -2194,9 +2150,7 @@
       <c r="M24" t="n">
         <v>0</v>
       </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/6497</t>
@@ -2268,9 +2222,7 @@
       <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/6242</t>
@@ -2342,9 +2294,7 @@
       <c r="M26" t="n">
         <v>0</v>
       </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/6500</t>
@@ -2416,9 +2366,7 @@
       <c r="M27" t="n">
         <v>0</v>
       </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/6588</t>
@@ -2490,9 +2438,7 @@
       <c r="M28" t="n">
         <v>0</v>
       </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/4037</t>
@@ -2564,9 +2510,7 @@
       <c r="M29" t="n">
         <v>0</v>
       </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/3897</t>
@@ -2638,9 +2582,7 @@
       <c r="M30" t="n">
         <v>0</v>
       </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/3891</t>
@@ -2712,9 +2654,7 @@
       <c r="M31" t="n">
         <v>0</v>
       </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
           <t>https://data.jxfz.gov.cn/openDate/directory/5201</t>
